--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.44</t>
+          <t>Application            app/PRAP.html v1.45</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.46.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.47.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.20.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.21.xlsx</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5946,6 +5946,28 @@
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Error - the figure is NOT applied. A project month is shared out among the people on it, so there is nobody to give this to; applying it anyway would give the project a total that none of its people account for, which is exactly the disagreement REQ-CAL-18 scales the people to avoid. Assign somebody to those months, or remove the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>V-33</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>A manual ASSIGNMENT figure that the project's own manual figure overrode. REQ-CAL-18 makes the project figure the mother figure - it is the whole month, and the people on it are scaled so they still add up to it - so somebody can type 2.00 against their own name and be given 1.73, because their figure and a colleague's together had to come to the project's month. That is the specified behaviour and it is what keeps the two utilisation charts agreeing; what was missing is that the application did it SILENTLY, so the sheet said one thing and the chart another with nothing connecting them. Now: a SOFT STOP at the moment the figure is edited, naming both numbers and offering to keep it or put it back; the cell marked; the Monthly estimation panel carrying a table of stated against given; and this finding, which reaches the findings report and the archived change log. WARNING, not error, and it never refuses: both numbers were typed deliberately and which of them is wrong is not the application's judgement.</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.45</t>
+          <t>Application            app/PRAP.html v1.46</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-05</t>
+          <t>Generated              2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.47.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.48.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.21.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.22.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.46</t>
+          <t>Application            app/PRAP.html v1.47</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.48.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.49.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.22.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.23.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.47</t>
+          <t>Application            app/PRAP.html v1.48</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-06</t>
+          <t>Generated              2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.49.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.50.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.23.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.24.xlsx</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5968,6 +5968,28 @@
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>V-34</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>A project whose month is not what its own standard says it needs - standard FTE x period weight x the part of the month it runs - in either direction. Raised from the CALCULATION, one finding per project, naming the months and the worst of them.</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Warning - it reports and never refuses. refuses() acts only on errors, so this reaches the findings report, the load banner, the archived change log and the results export without gating a save or asking a question. Departing from the standard is the POINT of a manual figure (REQ-CAL-18): a manager part way through a trial knows better than the assumptions, and the application has no business calling that wrong. What it does have business doing is saying so, because the departure is otherwise completely silent - the charts just draw a different project. An all-automatic plan raises nothing at all, which is what keeps the rule worth reading.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.48</t>
+          <t>Application            app/PRAP.html v1.49</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.50.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.51.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.24.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.25.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.49</t>
+          <t>Application            app/PRAP.html v1.50</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-11</t>
+          <t>Generated              2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.51.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.52.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.25.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.26.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.14.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.15.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.16.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.17.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.8.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.9.xlsx</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5990,6 +5990,28 @@
       <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Warning - it reports and never refuses. refuses() acts only on errors, so this reaches the findings report, the load banner, the archived change log and the results export without gating a save or asking a question. Departing from the standard is the POINT of a manual figure (REQ-CAL-18): a manager part way through a trial knows better than the assumptions, and the application has no business calling that wrong. What it does have business doing is saying so, because the departure is otherwise completely silent - the charts just draw a different project. An all-automatic plan raises nothing at all, which is what keeps the rule worth reading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>V-35</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Person.capacity_fte outside 0.00 to 1.00, in either direction.</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Error - and it REFUSES, which almost nothing else in this application does. capacity_fte is how much of ONE PERSON there is: 1.00 is full-time, 0.50 is half a week, 0.00 is somebody on the books who is not available at all and is therefore allowed. Every other figure here is a judgement somebody is entitled to make - a period weight, a role factor, a stated month - and the rules about those report rather than refuse, because which of two deliberate numbers is wrong is not the application's business. This is not a judgement: there is no such thing as one and a half of a person, the number is in the wrong unit, and the usual cause is hours typed into an FTE column - which the message says, with the arithmetic. Somebody doing the work of two people is TWO ASSIGNMENTS, or a person weight above 1.00 on one of them. A workbook that already breaks it still OPENS: the save and edit checks compare the count of blocking findings before and after, so a rule broken by an incoming file is reported without locking anybody out of their own plan. V-22 stands down on the same row - reporting that 1.50 is also not below the under-allocation floor would be true and useless.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.52.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.53.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.26.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.27.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  11</t>
+          <t>Source schema version  12</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.53.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.54.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.27.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.28.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.15.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.16.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.17.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.18.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.9.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.10.xlsx</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1954,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>edited_at</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -4451,24 +4451,24 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>When it was last set. The application fills this in.</t>
+          <t>Why this figure was stated.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4479,7 +4479,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Why this figure was stated.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -4507,7 +4507,7 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -4535,24 +4535,24 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -4563,7 +4563,7 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>Setting name.</t>
         </is>
       </c>
     </row>
@@ -4575,12 +4575,12 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4591,7 +4591,7 @@
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Setting value.</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -4618,34 +4618,6 @@
       </c>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>Setting value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -6075,7 +6047,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-12</t>
+          <t>Generated              2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.54.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.55.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.55.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.56.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.56.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.57.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.57.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.58.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.28.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.29.xlsx</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v1.0.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.1.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.58.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.59.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.29.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.30.xlsx</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5984,6 +5984,28 @@
       <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Error - and it REFUSES, which almost nothing else in this application does. capacity_fte is how much of ONE PERSON there is: 1.00 is full-time, 0.50 is half a week, 0.00 is somebody on the books who is not available at all and is therefore allowed. Every other figure here is a judgement somebody is entitled to make - a period weight, a role factor, a stated month - and the rules about those report rather than refuse, because which of two deliberate numbers is wrong is not the application's business. This is not a judgement: there is no such thing as one and a half of a person, the number is in the wrong unit, and the usual cause is hours typed into an FTE column - which the message says, with the arithmetic. Somebody doing the work of two people is TWO ASSIGNMENTS, or a person weight above 1.00 on one of them. A workbook that already breaks it still OPENS: the save and edit checks compare the count of blocking findings before and after, so a rule broken by an incoming file is reported without locking anybody out of their own plan. V-22 stands down on the same row - reporting that 1.50 is also not below the under-allocation floor would be true and useless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>V-36</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>A project that has periods and NOBODY ASSIGNED TO IT AT ALL. Raised from the CALCULATION, one finding per project, carrying what the project needs: the total FTE-months, the span, the peak and the month it falls in.</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS AN ABSENCE, NOT AN ERROR. Until the first assignment exists the application showed NOTHING for the project - no row in Resource by project, no band on either chart, no contribution to any tile - while still drawing it on the timeline, which reads the project's own dates. So the screen said the project exists and when it runs, and then declined to say what it costs, although type, phase, scope and periods are all the standard needs to say so. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS AN ABSENCE, NOT AN ERROR. Until the first assignment exists the application showed NOTHING for the project - no row in Resource by project, no band on either chart, no contribution to any tile - while still drawing it on the timeline, which reads the project's own dates. So the screen said the project exists and when it runs, and then declined to say what it costs, although type, phase, scope and periods are all the standard needs to say so. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
+          <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS A ROW OF BLANKS, NOT AN ERROR. The project IS listed - it has a row in Resource by project, it is drawn on the timeline, and it counts in the projects tile - but every one of its months is EMPTY, it puts nothing on the three demand charts, it takes no legend entry and it reaches no line of Standard vs staffed. That is worse than being absent: a row of blanks reads as a project that costs nothing rather than one nobody has been put on yet, which is the same failure V-34 exists for. Type, phase, scope and periods are all the standard needs to say what it costs. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.50</t>
+          <t>Application            app/PRAP.html v1.51</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.59.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.60.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.30.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.31.xlsx</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.1.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.2.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-13</t>
+          <t>Generated              2026-09-14</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>If they are still 1.00, say so before quoting any figure. The load formula then reduces to person_weight x month_coverage, which is a real number but not a resourced estimate.</t>
+          <t>If they are still 1.00, say so before quoting any figure. Each project's month then reduces to its own period_weight x month_run, which is a real number but not a resourced estimate - the shape is the user's, the magnitude is a placeholder.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Every seeded weight and role factor is 1.00 and says so in its note. They are NOT a company standard. If a user hands you a plan started this way, check whether those figures are still 1.00 before reading the FTE totals as real - until they are set, the load reduces to person_weight x month_coverage.</t>
+          <t>Every seeded weight and role factor is 1.00 and says so in its note. They are NOT a company standard. If a user hands you a plan started this way, check whether those figures are still 1.00 before reading the FTE totals as real - until they are set, a project's month reduces to its own period_weight x month_run, and the people on it still divide that between them. The figures then have a relative shape with no resourced magnitude behind them.</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4857,7 +4857,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>monthly_load_fte = period_weight x role_factor x person_weight x month_coverage   —   FTE. 1.00 FTE is fte_hours_per_month hours (Config, default 160 = 8 h/day x 5 days/week x 4 weeks). The dashboard can show hours instead; the stored numbers are always FTE.</t>
+          <t>A project's month is its OWN demand, and the people on it divide that month between them (REQ-CAL-19 as amended by R-32). The four per-assignment factors decide a SHARE, never a total.   —   FTE. 1.00 FTE is fte_hours_per_month hours (Config, default 160 = 8 h/day x 5 days/week x 4 weeks). The dashboard can show hours instead; the stored numbers are always FTE.</t>
         </is>
       </c>
     </row>
@@ -4876,82 +4876,156 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>period_weight</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ProjectPeriod.weight of the period containing the FIRST DAY of the month, for the assignment's project. A month in no period uses 1.00 and is reported under V-12.</t>
+          <t>demand(project, month)   = standard_fte( project, month ) x period_weight x month_run
+claim(assignment, month) = ( role_factor / sharers ) x person_weight x coverage
+fte(assignment, month)   = demand x claim / SUM( claims on that project-month )</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>role_factor</t>
+          <t>DO NOT</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>RoleFactor.role_factor for (project_type, clinical_phase, period_name, role_name). clinical_phase is null for 'Others' projects. A missing factor is an error under V-23 - the calculation would otherwise silently use 1.00.</t>
+          <t>Do NOT multiply period_weight x role_factor x person_weight x coverage and call the result FTE. That product is the CLAIM - a share weight, not a workload - and using it as a load is the single most common way to arrive at figures the application does not agree with. If you need a number, run tools/prap_io.py calculate rather than re-deriving it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>conserved</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Assignment.person_weight, UNLESS a PersonPeriodWeight window contains the first day of the month, in which case weight_override REPLACES it. It does not multiply it.</t>
+          <t>Because the shares are normalised, a project-month equals the sum of its own people to the hundredth, however many people are on it - and changing one person's assignment changes everyone else's share of that project-month. The shares are handed out in whole cents by largest remainder, so the parts cannot come to anything but the whole.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>month_coverage</t>
+          <t>standard_fte</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>the fraction of that calendar month's days the assignment actually spans, inclusive of both end dates: (min(month_end, assign_end) - max(month_start, assign_start) + 1 days) / days_in_month.</t>
+          <t>PeriodFTEStandard.standard_fte for (project_type, clinical_phase, scope, period_name). THIS IS WHAT SETS THE SIZE of the project's month - a monthly FTE for a project of this type, phase and scope in this period. Missing, it falls back to 1.00 and V-19 reports it, which degrades the month to its own period weight. Omitting this term is what makes a re-derived figure disagree with the application.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>assignment window</t>
+          <t>period_weight</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>assign_start_date .. assign_end_date. An empty assign_end_date means the project's end_date.</t>
+          <t>ProjectPeriod.weight of the period containing the FIRST DAY of the month, for the assignment's project. It ADJUSTS the standard up or down for this particular study; it is not the size on its own. A month in no period uses 1.00 and is reported under V-12.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>thresholds</t>
+          <t>month_run</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>over_allocation_fte and under_allocation_fte are ABSOLUTE FTE figures. They are NOT scaled by a person's capacity_fte (decision S2-01). under_allocation_min_months consecutive months below the floor make a run; a single low month is not flagged.</t>
+          <t>the part of the calendar month the PROJECT runs - the largest coverage among that project-month's assignments. It scales the demand, so a month the project only half occupies asks for half.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>role_factor</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>RoleFactor.role_factor for (project_type, clinical_phase, period_name, role_name). clinical_phase is null for 'Others' projects. It DIVIDES the month's demand between the roles actually staffed rather than adding to it. A missing factor is an error under V-23 - the calculation would otherwise silently use 1.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>sharers</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>how many people hold that role on that project in that month. The role's factor is divided among them, so two people in one role each claim half of it and the total is conserved; when one of them leaves, the other returns to a full share by themselves, with nobody editing anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>person_weight</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Assignment.person_weight, UNLESS a PersonPeriodWeight window contains the first day of the month, in which case weight_override REPLACES it. It does not multiply it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>the fraction of that calendar month's days the ASSIGNMENT actually spans, inclusive of both end dates: (min(month_end, assign_end) - max(month_start, assign_start) + 1 days) / days_in_month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>assignment window</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>assign_start_date .. assign_end_date. An empty assign_end_date means the project's end_date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>thresholds</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>over_allocation_fte and under_allocation_fte are ABSOLUTE FTE figures. They are NOT scaled by a person's capacity_fte (decision S2-01). under_allocation_min_months consecutive months below the floor make a run; a single low month is not flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>rows excluded</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>an assignment whose project or person does not exist, or which has no start date, contributes nothing and is reported instead.</t>
         </is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-14</t>
+          <t>Generated              2026-09-17</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.51</t>
+          <t>Application            app/PRAP.html v1.52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  12</t>
+          <t>Source schema version  13</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-17</t>
+          <t>Generated              2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.60.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.61.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.31.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.32.xlsx</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.16.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.17.xlsx</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.18.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.19.xlsx</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.10.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.11.xlsx</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1954,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>milestone_seq</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2876,10 +2876,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>milestone_highlight</t>
+        </is>
+      </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Display order on the timeline.</t>
+          <t>OPTIONAL. Marks this milestone on the Project timeline in a colour. Pick from the list; leave empty for no mark.</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2895,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>milestone_seq</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -2907,24 +2911,24 @@
       <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a date moved, or which inspection body.</t>
+          <t>Display order on the timeline.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>ProjectPeriod</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2935,7 +2939,7 @@
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>Free text. e.g. why a date moved, or which inspection body.</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2951,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -2963,7 +2967,7 @@
       <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2979,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>period_seq</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2991,7 +2995,7 @@
       <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Orders periods along the timeline. Unique within a project.</t>
+          <t>From the set for this project's type. UNIQUE within a project, so (project_id, period_name) is the key (R-11).</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3007,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>period_seq</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -3019,7 +3023,7 @@
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Orders periods along the timeline. Unique within a project.</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3035,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -3047,7 +3051,7 @@
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Inclusive. Periods must not overlap or leave a gap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3063,12 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -3075,7 +3079,7 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodFTEStandard.standard_fte does.</t>
+          <t>Inclusive. Periods must not overlap or leave a gap.</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3091,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -3103,24 +3107,24 @@
       <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a derived date was overridden by hand.</t>
+          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodFTEStandard.standard_fte does.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>PeriodFTEStandard</t>
+          <t>ProjectPeriod</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -3128,14 +3132,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
+          <t>Free text. e.g. why a derived date was overridden by hand.</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>The phase this standard applies to.</t>
+          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this standard applies to.</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
+          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>standard_fte</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3256,10 +3256,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>period_name_clinical</t>
+        </is>
+      </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. The STANDARD MONTHLY FTE a project of this type, phase and scope takes in this period - a magnitude, not a multiplier. 4.02 means the period costs about four full-time people a month. The project's own ProjectPeriod.weight then adjusts it up or down for that particular study, and the role factors divide it between the roles staffed.</t>
+          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3275,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>standard_fte</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3287,24 +3291,24 @@
       <c r="E48" s="8" t="inlineStr"/>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. the basis for this weight.</t>
+          <t>YOU SUPPLY. The STANDARD MONTHLY FTE a project of this type, phase and scope takes in this period - a magnitude, not a multiplier. 4.02 means the period costs about four full-time people a month. The project's own ProjectPeriod.weight then adjusts it up or down for that particular study, and the role factors divide it between the roles staffed.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>RoleFactor</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -3312,14 +3316,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Which type's role list this row belongs to.</t>
+          <t>Free text. e.g. the basis for this weight.</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
+          <t>Which type's role list this row belongs to.</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3408,10 +3408,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>work_scope_type</t>
+        </is>
+      </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>The period this factor applies to.</t>
+          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3427,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -3439,7 +3443,7 @@
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>The role.</t>
+          <t>The period this factor applies to.</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3455,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>role_factor</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3467,7 +3471,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
+          <t>The role.</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3483,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>absorbed_by</t>
+          <t>role_factor</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3495,7 +3499,7 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
+          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3511,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>role_note</t>
+          <t>absorbed_by</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -3523,24 +3527,24 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Basis for the factor.</t>
+          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>role_note</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3551,7 +3555,7 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>Basis for the factor.</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3567,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3579,7 +3583,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3607,7 +3611,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3623,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -3635,7 +3639,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3651,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3663,7 +3667,7 @@
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3679,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3691,7 +3695,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3707,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3731,12 +3735,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3747,7 +3751,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Blank = open.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -3773,7 +3777,11 @@
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -3783,7 +3791,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -3807,7 +3815,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -3831,7 +3839,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -3850,17 +3858,17 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3869,11 +3877,7 @@
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -3883,7 +3887,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -3899,7 +3903,7 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Person.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -3911,23 +3915,23 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -3939,23 +3943,23 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -3967,12 +3971,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3983,7 +3987,7 @@
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3999,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -4011,7 +4015,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Date the person joins. BLANK = the project's own start date.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -4039,7 +4043,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Date the person leaves. BLANK = the project's own end date.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4055,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -4067,7 +4071,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4083,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>estimation_type</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4095,7 +4099,7 @@
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
+          <t>How much this person works on this project, e.g. 0.40.</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4111,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>estimation_type</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -4123,7 +4127,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4139,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4149,7 +4153,11 @@
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -4159,7 +4167,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -4178,17 +4186,17 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4197,11 +4205,7 @@
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Foreign key to Assignment.</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -4211,12 +4215,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -4227,7 +4231,7 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4243,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -4255,7 +4259,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4271,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4283,7 +4287,7 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4299,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -4311,24 +4315,24 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4339,7 +4343,7 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>'project' or 'assignment' - which of the two this figure is for.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4355,12 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4367,7 +4371,7 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>The project_id or assignment_id it belongs to, per scope.</t>
+          <t>'project' or 'assignment' - which of the two this figure is for.</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4383,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -4395,7 +4399,7 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>The month, as YYYY-MM.</t>
+          <t>The project_id or assignment_id it belongs to, per scope.</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4411,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>fte</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -4423,7 +4427,7 @@
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>The monthly FTE, STATED rather than calculated.</t>
+          <t>The month, as YYYY-MM.</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4439,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>fte</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -4451,24 +4455,24 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Why this figure was stated.</t>
+          <t>The monthly FTE, STATED rather than calculated.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4479,7 +4483,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>Why this figure was stated.</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4495,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -4507,7 +4511,7 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4523,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -4535,24 +4539,24 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -4563,7 +4567,7 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
         </is>
       </c>
     </row>
@@ -4575,12 +4579,12 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4591,7 +4595,7 @@
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>Setting name.</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -4618,6 +4622,34 @@
       </c>
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4637,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4781,46 +4813,58 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>milestone_highlight</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
+          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Planning, Develop, Close</t>
+          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_others</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+          <t>Planning, Develop, Close</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>role_others</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Project lead, Main staff, Other staff</t>
         </is>
@@ -5224,7 +5268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6080,6 +6124,28 @@
       <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS A ROW OF BLANKS, NOT AN ERROR. The project IS listed - it has a row in Resource by project, it is drawn on the timeline, and it counts in the projects tile - but every one of its months is EMPTY, it puts nothing on the three demand charts, it takes no legend entry and it reaches no line of Standard vs staffed. That is worse than being absent: a row of blanks reads as a project that costs nothing rather than one nobody has been put on yet, which is the same failure V-34 exists for. Type, phase, scope and periods are all the standard needs to say what it costs. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>V-37</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Milestone.milestone_highlight carries a value that names no colour the application can draw.</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Warning - the milestone is drawn unmarked, which is what it would have been with the column empty, and the finding says so with the values the file's own Lists sheet offers. Never a refusal: a mark changes no figure, and a plan whose highlight column is misspelt is still a correct plan. It is reported rather than ignored because the failure is INVISIBLE otherwise - an unmarked milestone looks exactly like one nobody got round to marking, so a typo in the list value would quietly undo the thing the user asked for. What the application reads is the colour word inside the value ('red', 'yellow', 'blue', 'green', 'orange'), which is what lets a team write what their colour means beside it; the rule fires only when no such word is there at all.</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6209,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.52</t>
+          <t>Application            app/PRAP.html v1.53</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-09-23</t>
+          <t>Generated              2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.61.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.62.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.32.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.33.xlsx</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.2.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.3.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.53</t>
+          <t>Application            app/PRAP.html v1.54</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.62.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.63.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.33.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.34.xlsx</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.3.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.4.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.54</t>
+          <t>Application            app/PRAP.html v1.55</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.63.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.64.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.34.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.35.xlsx</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.4.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.5.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.55</t>
+          <t>Application            app/PRAP.html v1.56</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.64.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.65.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.35.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.36.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.56</t>
+          <t>Application            app/PRAP.html v1.57</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-01</t>
+          <t>Generated              2026-10-04</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1147,6 +1147,101 @@
       <c r="C38" s="8" t="inlineStr">
         <is>
           <t>do not send a .prap.json to a person expecting a spreadsheet - convert it to .xlsx first, unless they asked for the JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Diagnose a plan, recommend changes, or answer a what-if question</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>when</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>You are handed the calculated-FTE export (or the source plan) and asked how healthy the assignments are, what to change, or what happens if something changes. docs/PRAP_AI_Analysis_Guide.md is the full method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Score it in code: python tools/prap_analyze.py score &lt;file&gt; --out &lt;dir&gt;. It reads the export or a source plan and writes scorecard.json and scorecard.md - the 0-100 score, its five components with their inputs, the projects short, over or unallocated, the people over the ceiling, the next six months, and candidate moves with spare capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Explain the scorecard; do not recompute it. Every figure you quote must be in it or in the export, with the project, person and months it belongs to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>For any change - a recommendation you want to stand behind, a new project, a person leaving - edit the SOURCE plan (prap_io.py to-json), validate it, and run python tools/prap_analyze.py compare &lt;before&gt; &lt;after&gt;. Report the change in score and in the rows it moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>do NOT</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>do not add up Detail.demand_fte - it repeats the project's demand on every person's row; use ProjectMonth.demand_fte</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>do NOT</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>do not compute FTE yourself for a scenario - absorption, sharers, rounding and manual scaling make that wrong; run the engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>do NOT</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>do not present a candidate move as a result until compare has run on it</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1260,46 +1355,58 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>row insert/delete/identity</t>
+          <t>scorecard identical from the export and from the source</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>python tools/test_rows.py</t>
+          <t>python tools/test_analyze.py</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>type-ahead value lists</t>
+          <t>row insert/delete/identity</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>python tools/test_valuelist.py</t>
+          <t>python tools/test_rows.py</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>type-ahead value lists</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>python tools/test_charts.py</t>
+          <t>python tools/test_valuelist.py</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>charts</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>python tools/test_charts.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>text contrast</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>python tools/test_contrast.py</t>
         </is>
@@ -1463,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.65.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.66.xlsx</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.36.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.37.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.57</t>
+          <t>Application            app/PRAP.html v1.58</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-04</t>
+          <t>Generated              2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.66.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.67.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.37.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.38.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-07</t>
+          <t>Generated              2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.67.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.68.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.68.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.69.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.58</t>
+          <t>Application            app/PRAP.html v1.59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  13</t>
+          <t>Source schema version  14</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.69.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.70.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.38.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.39.xlsx</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.5.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.6.xlsx</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.17.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.18.xlsx</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.19.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.20.xlsx</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.11.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.12.xlsx</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2061,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -3211,10 +3211,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>period_highlight</t>
+        </is>
+      </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodFTEStandard.standard_fte does.</t>
+          <t>OPTIONAL. The colour this period is drawn in on the Project timeline. Pick from the list; leave empty and it is drawn gray.</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -3242,24 +3246,24 @@
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. why a derived date was overridden by hand.</t>
+          <t>THIS PROJECT'S OWN ADJUSTMENT to the standard for its type, phase and scope (REQ-CAL-19). 1.00 means an ordinary project of its kind; 1.20 means this one takes a fifth more. It does NOT carry the magnitude - PeriodFTEStandard.standard_fte does.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>PeriodFTEStandard</t>
+          <t>ProjectPeriod</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3267,14 +3271,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E44" s="8" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
+          <t>Free text. e.g. why a derived date was overridden by hand.</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>The phase this standard applies to.</t>
+          <t>A clinical trial type. 'Others' projects take manual weights instead.</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this standard applies to.</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
+          <t>The work scope this standard applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>standard_fte</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3395,10 +3395,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>period_name_clinical</t>
+        </is>
+      </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. The STANDARD MONTHLY FTE a project of this type, phase and scope takes in this period - a magnitude, not a multiplier. 4.02 means the period costs about four full-time people a month. The project's own ProjectPeriod.weight then adjusts it up or down for that particular study, and the role factors divide it between the roles staffed.</t>
+          <t>One of the seven clinical periods. Unique within a project (R-11).</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3414,12 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>standard_fte</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -3426,24 +3430,24 @@
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. the basis for this weight.</t>
+          <t>YOU SUPPLY. The STANDARD MONTHLY FTE a project of this type, phase and scope takes in this period - a magnitude, not a multiplier. 4.02 means the period costs about four full-time people a month. The project's own ProjectPeriod.weight then adjusts it up or down for that particular study, and the role factors divide it between the roles staffed.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>RoleFactor</t>
+          <t>PeriodFTEStandard</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3451,14 +3455,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
+      <c r="E50" s="8" t="inlineStr"/>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Which type's role list this row belongs to.</t>
+          <t>Free text. e.g. the basis for this weight.</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>clinical_phase</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
+          <t>Which type's role list this row belongs to.</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>work_scope_type</t>
+          <t>clinical_phase</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
+          <t>The phase this factor applies to. Leave EMPTY for 'Others'.</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>period_name</t>
+          <t>work_scope_type</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -3547,10 +3547,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>work_scope_type</t>
+        </is>
+      </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>The period this factor applies to.</t>
+          <t>The work scope this factor applies to. LEAVE EMPTY for a row that applies to EVERY scope - fill only the scopes that really differ.</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3566,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -3578,7 +3582,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>The role.</t>
+          <t>The period this factor applies to.</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3594,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>role_factor</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3606,7 +3610,7 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
+          <t>The role.</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3622,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>absorbed_by</t>
+          <t>role_factor</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3634,7 +3638,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
+          <t>YOU SUPPLY. Relative burden of this role in this period.</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3650,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>role_note</t>
+          <t>absorbed_by</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -3662,24 +3666,24 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Basis for the factor.</t>
+          <t>If NOBODY holds this role on a project, which role picks the work up. Blank = the work is simply not counted. See the README.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>RoleFactor</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>role_note</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3690,7 +3694,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>Basis for the factor.</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3706,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -3718,7 +3722,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3734,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -3746,7 +3750,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3762,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3774,7 +3778,7 @@
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3790,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -3802,7 +3806,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3818,12 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3830,7 +3834,7 @@
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -3870,12 +3874,12 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3886,7 +3890,7 @@
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Blank = open.</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3902,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -3912,7 +3916,11 @@
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -3922,7 +3930,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -3946,7 +3954,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -3970,7 +3978,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -3989,17 +3997,17 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -4008,11 +4016,7 @@
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -4038,7 +4042,7 @@
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Person.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -4050,23 +4054,23 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -4078,23 +4082,23 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4110,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -4122,7 +4126,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4138,12 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4150,7 +4154,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Date the person joins. BLANK = the project's own start date.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -4178,7 +4182,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Date the person leaves. BLANK = the project's own end date.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4194,12 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4206,7 +4210,7 @@
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4222,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>estimation_type</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -4234,7 +4238,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
+          <t>How much this person works on this project, e.g. 0.40.</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4250,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>estimation_type</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4262,7 +4266,7 @@
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -4288,7 +4292,11 @@
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr"/>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -4298,7 +4306,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4317,17 +4325,17 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -4336,11 +4344,7 @@
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>Foreign key to Assignment.</t>
-        </is>
-      </c>
+      <c r="F82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -4350,12 +4354,12 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4366,7 +4370,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Inclusive.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4382,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -4394,7 +4398,7 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4410,12 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4422,7 +4426,7 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4438,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -4450,24 +4454,24 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4478,7 +4482,7 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>'project' or 'assignment' - which of the two this figure is for.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4494,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -4506,7 +4510,7 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>The project_id or assignment_id it belongs to, per scope.</t>
+          <t>'project' or 'assignment' - which of the two this figure is for.</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4522,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -4534,7 +4538,7 @@
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>The month, as YYYY-MM.</t>
+          <t>The project_id or assignment_id it belongs to, per scope.</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4550,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>fte</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -4562,7 +4566,7 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>The monthly FTE, STATED rather than calculated.</t>
+          <t>The month, as YYYY-MM.</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4578,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>fte</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -4590,24 +4594,24 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Why this figure was stated.</t>
+          <t>The monthly FTE, STATED rather than calculated.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -4618,7 +4622,7 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>Why this figure was stated.</t>
         </is>
       </c>
     </row>
@@ -4630,12 +4634,12 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4646,7 +4650,7 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4662,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -4674,24 +4678,24 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4702,7 +4706,7 @@
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4718,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -4730,7 +4734,7 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>Setting name.</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4746,7 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -4757,6 +4761,34 @@
       </c>
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4776,7 +4808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4932,46 +4964,58 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
+          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Planning, Develop, Close</t>
+          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_others</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+          <t>Planning, Develop, Close</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>role_others</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Project lead, Main staff, Other staff</t>
         </is>
@@ -5375,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6253,6 +6297,28 @@
       <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Warning - the milestone is drawn unmarked, which is what it would have been with the column empty, and the finding says so with the values the file's own Lists sheet offers. Never a refusal: a mark changes no figure, and a plan whose highlight column is misspelt is still a correct plan. It is reported rather than ignored because the failure is INVISIBLE otherwise - an unmarked milestone looks exactly like one nobody got round to marking, so a typo in the list value would quietly undo the thing the user asked for. What the application reads is the colour word inside the value ('red', 'yellow', 'blue', 'green', 'orange'), which is what lets a team write what their colour means beside it; the rule fires only when no such word is there at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>V-38</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>ProjectPeriod.period_highlight carries a value that names no colour the application can draw.</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Warning - the period is drawn gray, which is what it would have been with the column empty, and the finding says so with the values the file's own Lists sheet offers. The period twin of V-37, for the same reason: a gray period looks exactly like one nobody chose a colour for, so a typo would quietly undo what the user asked for. Never a refusal - a colour changes no figure.</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6382,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.59</t>
+          <t>Application            app/PRAP.html v1.60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  14</t>
+          <t>Source schema version  15</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.70.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.71.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.39.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.40.xlsx</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.6.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.7.xlsx</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.18.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.19.xlsx</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.20.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.21.xlsx</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.12.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.13.xlsx</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1870,12 +1870,12 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>PeriodHighlight</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1894,33 +1894,33 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
@@ -1930,7 +1930,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1940,27 +1940,27 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>assignment_id, period_start</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Project|Assignment</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>scope, ref_id, month</t>
+          <t>assignment_id, period_start</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1990,60 +1990,90 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
+          <t>Project|Assignment</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>scope, ref_id, month</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>list_name, value</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>list_name, value</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>settings</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2061,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3701,12 +3731,12 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>PeriodHighlight</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>period_name</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3722,19 +3752,19 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Unique key, e.g. PSN-001.</t>
+          <t>A period name, from either period set. One row per name.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>PeriodHighlight</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -3747,22 +3777,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>period_highlight</t>
+        </is>
+      </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>The colour every project's period of this name is drawn in. Pick from the list; leave empty and it is drawn gray unless a project chooses a colour for its own period.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>PeriodHighlight</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3778,7 +3812,7 @@
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Grouping for the dashboard.</t>
+          <t>Free text. e.g. what the colour is meant to say.</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3824,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>primary_role</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3806,7 +3840,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Usual role; an assignment can override it.</t>
+          <t>Unique key, e.g. PSN-001.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3852,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>capacity_fte</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3834,7 +3868,7 @@
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
+          <t>Display name.</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3880,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>employment_start</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3862,7 +3896,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Grouping for the dashboard.</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3908,12 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>employment_end</t>
+          <t>primary_role</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3890,7 +3924,7 @@
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Blank = open.</t>
+          <t>Usual role; an assignment can override it.</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3936,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>capacity_fte</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -3918,7 +3952,7 @@
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Available capacity. 1.00 = full time. Lower for a part-timer.</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3964,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>employment_start</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3944,7 +3978,11 @@
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Blank = open.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -3954,12 +3992,12 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>employment_end</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3968,7 +4006,11 @@
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Blank = open.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -3978,7 +4020,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>note_4</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -3992,7 +4034,11 @@
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
-      <c r="F69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -4002,7 +4048,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>note_5</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -4021,17 +4067,17 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -4040,26 +4086,22 @@
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Unique key. One row per person + project + role.</t>
-        </is>
-      </c>
+      <c r="F71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -4068,39 +4110,31 @@
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Foreign key to Person.</t>
-        </is>
-      </c>
+      <c r="F72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>DERIVED - looked up from Person, do not type.</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -4110,7 +4144,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -4126,7 +4160,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Foreign key to Project.</t>
+          <t>Unique key. One row per person + project + role.</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4172,12 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4154,7 +4188,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Must exist in RoleFactor for this project's type.</t>
+          <t>Foreign key to Person.</t>
         </is>
       </c>
     </row>
@@ -4166,23 +4200,23 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>assign_start_date</t>
+          <t>person_name</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Date the person joins. BLANK = the project's own start date.</t>
+          <t>DERIVED - looked up from Person, do not type.</t>
         </is>
       </c>
     </row>
@@ -4194,12 +4228,12 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>assign_end_date</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4210,7 +4244,7 @@
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Date the person leaves. BLANK = the project's own end date.</t>
+          <t>Foreign key to Project.</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4256,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>person_weight</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -4238,7 +4272,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>How much this person works on this project, e.g. 0.40.</t>
+          <t>Must exist in RoleFactor for this project's type.</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4284,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>estimation_type</t>
+          <t>assign_start_date</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4266,7 +4300,7 @@
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
+          <t>Date the person joins. BLANK = the project's own start date.</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4312,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>assign_end_date</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -4294,7 +4328,7 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Date the person leaves. BLANK = the project's own end date.</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4340,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>person_weight</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4320,7 +4354,11 @@
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>How much this person works on this project, e.g. 0.40.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -4330,7 +4368,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>estimation_type</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -4344,22 +4382,26 @@
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>'automatic' (default) or 'manual'. Manual means the monthly FTE for THIS ASSIGNMENT is stated on MonthlyEstimate rather than calculated.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4370,24 +4412,24 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Foreign key to Assignment.</t>
+          <t>Free text.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4396,26 +4438,22 @@
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr"/>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>Inclusive.</t>
-        </is>
-      </c>
+      <c r="F84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>PersonPeriodWeight</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4424,11 +4462,7 @@
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr"/>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Inclusive. Windows within one assignment must not overlap.</t>
-        </is>
-      </c>
+      <c r="F85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -4438,12 +4472,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>weight_override</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4454,7 +4488,7 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>REPLACES person_weight for these months - it does not multiply it.</t>
+          <t>Foreign key to Assignment.</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4500,12 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4482,24 +4516,24 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Why the weight differs.</t>
+          <t>Inclusive.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>period_end</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -4510,19 +4544,19 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>'project' or 'assignment' - which of the two this figure is for.</t>
+          <t>Inclusive. Windows within one assignment must not overlap.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>weight_override</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -4538,19 +4572,19 @@
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>The project_id or assignment_id it belongs to, per scope.</t>
+          <t>REPLACES person_weight for these months - it does not multiply it.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>MonthlyEstimate</t>
+          <t>PersonPeriodWeight</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -4566,7 +4600,7 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>The month, as YYYY-MM.</t>
+          <t>Why the weight differs.</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4612,12 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>fte</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4594,7 +4628,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>The monthly FTE, STATED rather than calculated.</t>
+          <t>'project' or 'assignment' - which of the two this figure is for.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4640,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -4622,24 +4656,24 @@
       <c r="E92" s="8" t="inlineStr"/>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Why this figure was stated.</t>
+          <t>The project_id or assignment_id it belongs to, per scope.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4650,19 +4684,19 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>The month, as YYYY-MM.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>fte</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -4678,14 +4712,14 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>The monthly FTE, STATED rather than calculated.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>MonthlyEstimate</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -4706,19 +4740,19 @@
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>Why this figure was stated.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>list_name</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -4734,14 +4768,14 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Which list this value belongs to.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -4762,19 +4796,19 @@
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -4789,6 +4823,90 @@
       </c>
       <c r="E98" s="8" t="inlineStr"/>
       <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Setting name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -5419,7 +5537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6319,6 +6437,28 @@
       <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Warning - the period is drawn gray, which is what it would have been with the column empty, and the finding says so with the values the file's own Lists sheet offers. The period twin of V-37, for the same reason: a gray period looks exactly like one nobody chose a colour for, so a typo would quietly undo what the user asked for. Never a refusal - a colour changes no figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>V-39</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>A PeriodHighlight row cannot be applied: its value names no colour, its period name is given twice, or no period list knows the name.</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Warning - the period is drawn gray, or on its first row's colour, which looks exactly like a choice nobody made, so it is said. Never a refusal: a colour changes no figure.</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6522,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,14 +540,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.60</t>
+          <t>Application            app/PRAP.html v1.61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Source schema version  15</t>
+          <t>Source schema version  16</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-08</t>
+          <t>Generated              2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.71.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.72.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.40.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.41.xlsx</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.7.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.8.xlsx</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.19.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.20.xlsx</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.21.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.22.xlsx</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.13.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.14.xlsx</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,60 +2020,90 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>project_id, month, issue</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>list_name, value</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F15" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>list_name, value</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>settings</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F17" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2091,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4747,12 +4777,12 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>list_name</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -4768,24 +4798,24 @@
       <c r="E96" s="8" t="inlineStr"/>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Which list this value belongs to.</t>
+          <t>The project the issue is on.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -4796,24 +4826,24 @@
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>A permitted value. Add a row inside the block to extend a list.</t>
+          <t>The month, as YYYY-MM.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -4821,27 +4851,31 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>issue_kind</t>
+        </is>
+      </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>Free text. e.g. when a value was added, or what it means.</t>
+          <t>short / over / unstaffed - which way the month is off its standard.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -4849,22 +4883,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>issue_review_status</t>
+        </is>
+      </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Setting name.</t>
+          <t>Confirmed - no issue / Accepted (both close it: shown muted) / To be fixed (stays open, with this note).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>gap_fte</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -4880,19 +4918,19 @@
       <c r="E100" s="8" t="inlineStr"/>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Setting value.</t>
+          <t>The gap when it was reviewed (staffed - needed). If the gap moves, the review is shown as needing a fresh look.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>IssueReview</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>rationale</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -4907,6 +4945,230 @@
       </c>
       <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Why - the reason a reader will see whenever they open the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>IssueReview</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>reviewed_by</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr"/>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Who decided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>IssueReview</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>reviewed_at</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>When, as YYYY-MM-DD HH:MM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Which list this value belongs to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>A permitted value. Add a row inside the block to extend a list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>note_1</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Free text. e.g. when a value was added, or what it means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Setting name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr"/>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Setting value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>What it controls.</t>
         </is>
@@ -4926,7 +5188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5082,58 +5344,82 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>period_highlight</t>
+          <t>issue_review_status</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
+          <t>Confirmed - no issue, Accepted, To be fixed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>period_name_clinical</t>
+          <t>issue_kind</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
+          <t>short, over, unstaffed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>period_name_others</t>
+          <t>period_highlight</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Planning, Develop, Close</t>
+          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>role_clinical</t>
+          <t>period_name_clinical</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+          <t>Before-Start-up, Start-up, Conduct (interim), Close-out (interim), Conduct (final), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>period_name_others</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Planning, Develop, Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>role_clinical</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Project oversight, Lead data manager, Clinical Data Associator, Clinical Database Programmer, Data Analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>role_others</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Project lead, Main staff, Other staff</t>
         </is>
@@ -5537,7 +5823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6459,6 +6745,28 @@
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Warning - the period is drawn gray, or on its first row's colour, which looks exactly like a choice nobody made, so it is said. Never a refusal: a colour changes no figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>V-40</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>An IssueReview row no longer describes its month: the issue it reviewed has gone, or the month's gap is not the gap that was reviewed.</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Information - a gone issue's review is kept as history; a moved gap's review no longer closes the month, which is shown open and marked 're-check'. Never a refusal.</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6830,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-09</t>
+          <t>Generated              2026-10-10</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.61</t>
+          <t>Application            app/PRAP.html v1.62</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-10</t>
+          <t>Generated              2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.72.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.73.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.41.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.42.xlsx</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.20.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.21.xlsx</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.22.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.23.xlsx</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_10x10_v1.14.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_10x10_v1.15.xlsx</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
+          <t>Highlight (Red), Highlight (Orange), Highlight (Yellow), Highlight (Lime), Highlight (Green), Highlight (Teal), Highlight (Cyan), Highlight (Blue), Highlight (Navy), Highlight (Purple), Highlight (Magenta), Highlight (Pink), Highlight (Brown)</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Highlight (Red), Highlight (Yellow), Highlight (Blue), Highlight (Green), Highlight (Orange)</t>
+          <t>Highlight (Red), Highlight (Orange), Highlight (Yellow), Highlight (Lime), Highlight (Green), Highlight (Teal), Highlight (Cyan), Highlight (Blue), Highlight (Navy), Highlight (Purple), Highlight (Magenta), Highlight (Pink), Highlight (Brown)</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.62</t>
+          <t>Application            app/PRAP.html v1.63</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-11</t>
+          <t>Generated              2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.73.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.74.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.42.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.43.xlsx</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.8.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.9.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
+++ b/docs/PRAP_AI_Agent_Guide_v1.0.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Read_me_first" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Columns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Value_lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Periods" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Validation_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Interchange" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Recipes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_Ways_in" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Documents" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Application            app/PRAP.html v1.63</t>
+          <t>Application            app/PRAP.html v1.64</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated              2026-10-12</t>
+          <t>Generated              2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_Development_Plan_v2.74.xlsx</t>
+          <t>docs/PRAP_Development_Plan_v2.75.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>docs/PRAP_Programming_Specification_v1.43.xlsx</t>
+          <t>docs/PRAP_Programming_Specification_v1.44.xlsx</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>docs/PRAP_UI_Component_List_v2.9.xlsx</t>
+          <t>docs/PRAP_UI_Component_List_v2.10.xlsx</t>
         </is>
       </c>
     </row>
